--- a/artfynd/A 38646-2025 artfynd.xlsx
+++ b/artfynd/A 38646-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY34"/>
+  <dimension ref="A1:AY64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2324,10 +2324,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>134702573</v>
+        <v>134745796</v>
       </c>
       <c r="B19" t="n">
-        <v>79039</v>
+        <v>79405</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2335,37 +2335,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>353</v>
+        <v>185</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Flasktjärnslugnet, Flasktjärnslugnet, Dlr</t>
+          <t>Husknoppen, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>487967</v>
+        <v>487907</v>
       </c>
       <c r="R19" t="n">
-        <v>6825231</v>
+        <v>6825248</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2392,9 +2392,19 @@
           <t>2026-06-27</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>16:47</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2409,22 +2419,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>134703642</v>
+        <v>134745797</v>
       </c>
       <c r="B20" t="n">
-        <v>79039</v>
+        <v>79405</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2432,37 +2442,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>353</v>
+        <v>185</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Husknoppen, Husknoppen, Dlr</t>
+          <t>Husknoppen, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>488222</v>
+        <v>487943</v>
       </c>
       <c r="R20" t="n">
-        <v>6825108</v>
+        <v>6825236</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2489,9 +2499,19 @@
           <t>2026-06-27</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>16:50</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2506,22 +2526,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>134702389</v>
+        <v>134745800</v>
       </c>
       <c r="B21" t="n">
-        <v>80489</v>
+        <v>79405</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2529,37 +2549,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2081</v>
+        <v>185</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Flasktjärnslugnet, Flasktjärnslugnet, Dlr</t>
+          <t>Husknoppen, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>487896</v>
+        <v>487980</v>
       </c>
       <c r="R21" t="n">
-        <v>6825229</v>
+        <v>6825220</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2586,9 +2606,19 @@
           <t>2026-06-27</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>16:56</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2603,22 +2633,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>134703715</v>
+        <v>134745801</v>
       </c>
       <c r="B22" t="n">
-        <v>93271</v>
+        <v>79405</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2626,34 +2656,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>185</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Flasktjärnslugnet, Flasktjärnslugnet, Dlr</t>
+          <t>Husknoppen, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>488237</v>
+        <v>487988</v>
       </c>
       <c r="R22" t="n">
-        <v>6825112</v>
+        <v>6825227</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2683,9 +2713,19 @@
           <t>2026-06-27</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>16:58</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2700,60 +2740,60 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>134702339</v>
+        <v>134745803</v>
       </c>
       <c r="B23" t="n">
-        <v>79373</v>
+        <v>79405</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Flasktjärnslugnet, Flasktjärnslugnet, Dlr</t>
+          <t>Husknoppen, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>487903</v>
+        <v>488001</v>
       </c>
       <c r="R23" t="n">
-        <v>6825242</v>
+        <v>6825221</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2780,9 +2820,19 @@
           <t>2026-06-27</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2797,60 +2847,60 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>134702985</v>
+        <v>134745810</v>
       </c>
       <c r="B24" t="n">
-        <v>79373</v>
+        <v>79405</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Flasktjärnslugnet, Flasktjärnslugnet, Dlr</t>
+          <t>Husknoppen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>488083</v>
+        <v>488036</v>
       </c>
       <c r="R24" t="n">
-        <v>6825180</v>
+        <v>6825217</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2877,9 +2927,19 @@
           <t>2026-06-27</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>17:07</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2894,60 +2954,60 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>134703062</v>
+        <v>134745812</v>
       </c>
       <c r="B25" t="n">
-        <v>79373</v>
+        <v>79405</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Husknoppen, Husknoppen, Dlr</t>
+          <t>Husknoppen, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>488113</v>
+        <v>488074</v>
       </c>
       <c r="R25" t="n">
-        <v>6825138</v>
+        <v>6825186</v>
       </c>
       <c r="S25" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -2974,9 +3034,19 @@
           <t>2026-06-27</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>17:11</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -2991,60 +3061,60 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>134703403</v>
+        <v>134745814</v>
       </c>
       <c r="B26" t="n">
-        <v>79373</v>
+        <v>79405</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Husknoppen, Husknoppen, Dlr</t>
+          <t>Husknoppen, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>488218</v>
+        <v>488147</v>
       </c>
       <c r="R26" t="n">
-        <v>6825055</v>
+        <v>6825163</v>
       </c>
       <c r="S26" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3071,9 +3141,19 @@
           <t>2026-06-27</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>17:18</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3088,60 +3168,60 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>134703640</v>
+        <v>134745816</v>
       </c>
       <c r="B27" t="n">
-        <v>79373</v>
+        <v>79405</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Flasktjärnslugnet, Flasktjärnslugnet, Dlr</t>
+          <t>Husknoppen, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>488221</v>
+        <v>488163</v>
       </c>
       <c r="R27" t="n">
-        <v>6825118</v>
+        <v>6825135</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3168,9 +3248,19 @@
           <t>2026-06-27</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>17:23</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3185,60 +3275,60 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>134703693</v>
+        <v>134745817</v>
       </c>
       <c r="B28" t="n">
-        <v>79373</v>
+        <v>79405</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Husknoppen, Husknoppen, Dlr</t>
+          <t>Husknoppen, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>488227</v>
+        <v>488184</v>
       </c>
       <c r="R28" t="n">
-        <v>6825124</v>
+        <v>6825130</v>
       </c>
       <c r="S28" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3265,9 +3355,19 @@
           <t>2026-06-27</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>17:26</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3282,60 +3382,60 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>134703770</v>
+        <v>134745819</v>
       </c>
       <c r="B29" t="n">
-        <v>79373</v>
+        <v>79405</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Flasktjärnslugnet, Flasktjärnslugnet, Dlr</t>
+          <t>Husknoppen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>488263</v>
+        <v>488198</v>
       </c>
       <c r="R29" t="n">
-        <v>6825101</v>
+        <v>6825137</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3362,9 +3462,19 @@
           <t>2026-06-27</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>17:34</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>17:34</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3379,22 +3489,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>134703777</v>
+        <v>134745820</v>
       </c>
       <c r="B30" t="n">
-        <v>79130</v>
+        <v>79405</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3402,37 +3512,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6446</v>
+        <v>185</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Husknoppen, Husknoppen, Dlr</t>
+          <t>Husknoppen, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>488272</v>
+        <v>488200</v>
       </c>
       <c r="R30" t="n">
-        <v>6825063</v>
+        <v>6825113</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3459,9 +3569,19 @@
           <t>2026-06-27</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>17:43</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3476,22 +3596,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>134703305</v>
+        <v>134745821</v>
       </c>
       <c r="B31" t="n">
-        <v>79992</v>
+        <v>79405</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3499,37 +3619,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Husknoppen, Husknoppen, Dlr</t>
+          <t>Husknoppen, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>488196</v>
+        <v>488235</v>
       </c>
       <c r="R31" t="n">
-        <v>6825112</v>
+        <v>6825100</v>
       </c>
       <c r="S31" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3556,9 +3676,19 @@
           <t>2026-06-27</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>17:49</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3573,22 +3703,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>134703637</v>
+        <v>134745823</v>
       </c>
       <c r="B32" t="n">
-        <v>79992</v>
+        <v>79405</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3596,37 +3726,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Husknoppen, Husknoppen, Dlr</t>
+          <t>Husknoppen, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>488222</v>
+        <v>488265</v>
       </c>
       <c r="R32" t="n">
-        <v>6825108</v>
+        <v>6825095</v>
       </c>
       <c r="S32" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3653,9 +3783,19 @@
           <t>2026-06-27</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>17:54</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3670,60 +3810,60 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>134702704</v>
+        <v>134745827</v>
       </c>
       <c r="B33" t="n">
-        <v>57162</v>
+        <v>79405</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100138</v>
+        <v>185</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Husknoppen, Husknoppen, Dlr</t>
+          <t>Husknoppen, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>487988</v>
+        <v>488302</v>
       </c>
       <c r="R33" t="n">
-        <v>6825213</v>
+        <v>6825073</v>
       </c>
       <c r="S33" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3750,14 +3890,19 @@
           <t>2026-06-27</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>18:03</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2026-06-27</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Spillning.</t>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3772,22 +3917,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>134703803</v>
+        <v>134745828</v>
       </c>
       <c r="B34" t="n">
-        <v>79131</v>
+        <v>79405</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3795,37 +3940,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Flasktjärnslugnet, Flasktjärnslugnet, Dlr</t>
+          <t>Husknoppen, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>488279</v>
+        <v>488332</v>
       </c>
       <c r="R34" t="n">
-        <v>6825109</v>
+        <v>6825082</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3852,9 +3997,19 @@
           <t>2026-06-27</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>18:05</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3869,15 +4024,3094 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>134702573</v>
+      </c>
+      <c r="B35" t="n">
+        <v>79039</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>353</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Flasktjärnslugnet, Flasktjärnslugnet, Dlr</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>487967</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6825231</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
           <t>Anders Heggestad</t>
         </is>
       </c>
-      <c r="AX34" t="inlineStr">
+      <c r="AX35" t="inlineStr">
         <is>
           <t>Anders Heggestad</t>
         </is>
       </c>
-      <c r="AY34" t="inlineStr"/>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>134703642</v>
+      </c>
+      <c r="B36" t="n">
+        <v>79039</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>353</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Husknoppen, Husknoppen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>488222</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6825108</v>
+      </c>
+      <c r="S36" t="n">
+        <v>20</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>134702389</v>
+      </c>
+      <c r="B37" t="n">
+        <v>80489</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Flasktjärnslugnet, Flasktjärnslugnet, Dlr</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>487896</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6825229</v>
+      </c>
+      <c r="S37" t="n">
+        <v>5</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>134703715</v>
+      </c>
+      <c r="B38" t="n">
+        <v>93271</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Flasktjärnslugnet, Flasktjärnslugnet, Dlr</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>488237</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6825112</v>
+      </c>
+      <c r="S38" t="n">
+        <v>5</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>134702339</v>
+      </c>
+      <c r="B39" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Flasktjärnslugnet, Flasktjärnslugnet, Dlr</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>487903</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6825242</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>134702985</v>
+      </c>
+      <c r="B40" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Flasktjärnslugnet, Flasktjärnslugnet, Dlr</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>488083</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6825180</v>
+      </c>
+      <c r="S40" t="n">
+        <v>5</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>134703062</v>
+      </c>
+      <c r="B41" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Husknoppen, Husknoppen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>488113</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6825138</v>
+      </c>
+      <c r="S41" t="n">
+        <v>20</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>134703403</v>
+      </c>
+      <c r="B42" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Husknoppen, Husknoppen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>488218</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6825055</v>
+      </c>
+      <c r="S42" t="n">
+        <v>20</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>134703640</v>
+      </c>
+      <c r="B43" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Flasktjärnslugnet, Flasktjärnslugnet, Dlr</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>488221</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6825118</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>134703693</v>
+      </c>
+      <c r="B44" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Husknoppen, Husknoppen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>488227</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6825124</v>
+      </c>
+      <c r="S44" t="n">
+        <v>20</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>134703770</v>
+      </c>
+      <c r="B45" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Flasktjärnslugnet, Flasktjärnslugnet, Dlr</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>488263</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6825101</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>134745804</v>
+      </c>
+      <c r="B46" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Husknoppen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>488001</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6825221</v>
+      </c>
+      <c r="S46" t="n">
+        <v>5</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>134745813</v>
+      </c>
+      <c r="B47" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Husknoppen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>488093</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6825184</v>
+      </c>
+      <c r="S47" t="n">
+        <v>7</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>17:12</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>17:12</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>134745815</v>
+      </c>
+      <c r="B48" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Husknoppen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>488165</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6825136</v>
+      </c>
+      <c r="S48" t="n">
+        <v>9</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>134745822</v>
+      </c>
+      <c r="B49" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Husknoppen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>488237</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6825104</v>
+      </c>
+      <c r="S49" t="n">
+        <v>5</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>134745802</v>
+      </c>
+      <c r="B50" t="n">
+        <v>79397</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>6434</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Nästlav</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Bryoria furcellata</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Husknoppen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>488001</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6825221</v>
+      </c>
+      <c r="S50" t="n">
+        <v>5</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>134703777</v>
+      </c>
+      <c r="B51" t="n">
+        <v>79130</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Husknoppen, Husknoppen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>488272</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6825063</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>134745805</v>
+      </c>
+      <c r="B52" t="n">
+        <v>79130</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Husknoppen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>488005</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6825238</v>
+      </c>
+      <c r="S52" t="n">
+        <v>7</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>17:01</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>17:01</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>134745825</v>
+      </c>
+      <c r="B53" t="n">
+        <v>79130</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Husknoppen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>488267</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6825069</v>
+      </c>
+      <c r="S53" t="n">
+        <v>6</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>17:58</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>17:58</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>134703305</v>
+      </c>
+      <c r="B54" t="n">
+        <v>79992</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Husknoppen, Husknoppen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>488196</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6825112</v>
+      </c>
+      <c r="S54" t="n">
+        <v>20</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>134703637</v>
+      </c>
+      <c r="B55" t="n">
+        <v>79992</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Husknoppen, Husknoppen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>488222</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6825108</v>
+      </c>
+      <c r="S55" t="n">
+        <v>20</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>134745808</v>
+      </c>
+      <c r="B56" t="n">
+        <v>79992</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Husknoppen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>488037</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6825213</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>17:05</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>17:05</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>134702704</v>
+      </c>
+      <c r="B57" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Husknoppen, Husknoppen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>487988</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6825213</v>
+      </c>
+      <c r="S57" t="n">
+        <v>20</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Spillning.</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>134745826</v>
+      </c>
+      <c r="B58" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Husknoppen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>488298</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6825077</v>
+      </c>
+      <c r="S58" t="n">
+        <v>6</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>18:02</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>18:02</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>134745870</v>
+      </c>
+      <c r="B59" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Husknoppen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>488066</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6825164</v>
+      </c>
+      <c r="S59" t="n">
+        <v>5</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>20:56</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>20:56</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>134745830</v>
+      </c>
+      <c r="B60" t="n">
+        <v>99112</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Husknoppen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>488407</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6825083</v>
+      </c>
+      <c r="S60" t="n">
+        <v>9</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>18:14</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>18:14</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>100 plantor</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>134703803</v>
+      </c>
+      <c r="B61" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Flasktjärnslugnet, Flasktjärnslugnet, Dlr</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>488279</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6825109</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>134745818</v>
+      </c>
+      <c r="B62" t="n">
+        <v>79963</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Husknoppen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>488200</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6825138</v>
+      </c>
+      <c r="S62" t="n">
+        <v>8</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>17:34</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>17:34</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>134745824</v>
+      </c>
+      <c r="B63" t="n">
+        <v>79963</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Husknoppen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>488267</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6825069</v>
+      </c>
+      <c r="S63" t="n">
+        <v>6</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>17:56</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>17:56</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>134745829</v>
+      </c>
+      <c r="B64" t="n">
+        <v>79963</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Husknoppen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>488379</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6825089</v>
+      </c>
+      <c r="S64" t="n">
+        <v>7</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>18:12</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>18:12</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 38646-2025 artfynd.xlsx
+++ b/artfynd/A 38646-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY64"/>
+  <dimension ref="A1:AZ64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134702449</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134702672</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134702913</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134702956</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134703102</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134703118</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134703233</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134703356</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134703515</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134703544</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134703570</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134703798</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1933,6 +1998,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134703817</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2030,6 +2100,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134703837</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2127,6 +2202,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134703867</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2224,6 +2304,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134703926</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2321,6 +2406,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134704096</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2428,6 +2518,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134745796</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2535,6 +2630,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134745797</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2642,6 +2742,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134745800</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2749,6 +2854,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134745801</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2856,6 +2966,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134745803</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2963,6 +3078,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134745810</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3070,6 +3190,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134745812</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3177,6 +3302,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134745814</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3284,6 +3414,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134745816</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3391,6 +3526,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134745817</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3498,6 +3638,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134745819</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3605,6 +3750,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134745820</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3712,6 +3862,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134745821</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3819,6 +3974,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134745823</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3926,6 +4086,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134745827</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4033,6 +4198,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134745828</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4130,6 +4300,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134702573</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4227,6 +4402,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134703642</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4324,6 +4504,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134702389</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4421,6 +4606,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134703715</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4518,6 +4708,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134702339</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4615,6 +4810,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134702985</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4712,6 +4912,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134703062</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4809,6 +5014,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134703403</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4906,6 +5116,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134703640</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5003,6 +5218,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134703693</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5100,6 +5320,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134703770</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5207,6 +5432,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134745804</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5314,6 +5544,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134745813</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5421,6 +5656,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134745815</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5528,6 +5768,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134745822</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5635,6 +5880,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134745802</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5732,6 +5982,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134703777</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5839,6 +6094,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134745805</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5946,6 +6206,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134745825</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6043,6 +6308,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134703305</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6140,6 +6410,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134703637</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6247,6 +6522,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134745808</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6349,6 +6629,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134702704</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6461,6 +6746,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134745826</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6573,6 +6863,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134745870</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6694,6 +6989,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134745830</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6791,6 +7091,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134703803</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6898,6 +7203,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134745818</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7005,6 +7315,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134745824</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7112,8 +7427,78 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134745829</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>